--- a/MS Excel Crash Course/Lecture 14.xlsx
+++ b/MS Excel Crash Course/Lecture 14.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AR Boot Camp 2k26\MS Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AR Boot Camp 2k26\MS Excel Crash Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AE6991-4EA4-4A16-80A5-F6E8DB1154CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C2DB9A-8F7D-400E-943D-30E48794ACAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,9 +148,6 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -162,6 +159,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -452,144 +452,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C3" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="A3" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C3" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E3" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C4" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="A4" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C4" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E4" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C5" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="A5" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C5" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E5" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C6" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="A6" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C6" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E6" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C7" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="A7" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C7" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E7" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C8" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="A8" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C8" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E8" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C9" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="A9" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C9" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E9" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>923313771572</v>
-      </c>
-      <c r="C10" s="3">
-        <v>923313771572</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="A10" s="1">
+        <v>923313771572</v>
+      </c>
+      <c r="C10" s="2">
+        <v>923313771572</v>
+      </c>
+      <c r="E10" s="2">
         <v>923313771572</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>12345678910</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>123456789123</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
     </row>
